--- a/TP2026/TP10.xlsx
+++ b/TP2026/TP10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Documents\GitHub\u3\TP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FE9C62-BCC8-468E-AF07-1369376493A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9C123B-D060-47C4-906D-EF9DB66AEB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,8 +32,642 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Abdellah TAHTOH</author>
+  </authors>
+  <commentList>
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{9E68D656-7E28-4BED-B3A2-D6B7498D74CF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>📖 الوضعية: يمرّ زبون عبر صندوق الأداء. احسب مبلغ كل سلعة (الثمن × الكمية) ثم المجموع الإجمالي للوصل. اكتب صيغة واحدة فقط ثم انسخها!</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{F0B50828-307D-49DB-83F9-6551EE4312B9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>🔵 نوع المرجع: نسبي — لأن كل سطر له ثمنه الخاص وكميته الخاصة.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{02BEE335-2CCF-4CAB-9FB8-08673B7ADA14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>المنتوج</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{71B60A7C-DBB4-4EFA-A065-7B8559106F7F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الرواق</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{633C9472-EB3A-4A9F-8960-60BE311849EE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الثمن الوحدوي (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{B477F4E3-AE15-4B73-849C-BB6920E23A62}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الكمية</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{BF50B2AD-208B-41E1-B099-A49CDDFC5A98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>💰 المبلغ (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{49DEB1A7-4C0E-4B07-8B84-8020F92B7499}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>المجموع الواجب أداؤه</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{F9968B21-C51B-4BF8-B631-DF09CE326128}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>📖 الوضعية: اجتاز التلاميذ 3 اختبارات. المعاملات (1، 2، 3) مخزنة في خانات ثابتة. يجب عليك حساب المعدل المُرجَّح لكل تلميذ باستعمال صيغة واحدة فقط.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{11A4EE42-9923-423F-923F-761D7B7036A3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>🟢 نوع المرجع: مطلق — لأن المعاملات لا تتغير أبداً.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{27541602-0FF6-4A4C-9C54-F43367035067}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>معامل الفرض 1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{0A85C572-5E8C-4096-B829-9F3BA26A86DD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>معامل الفرض2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{B8C9BCC9-AD68-4836-999C-7BC574AC4E33}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>معامل الامتحان</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{D2E9BC74-E0A7-4FBA-97BA-66802609A265}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الفرض1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{F1D312CF-59B1-4745-AD13-2973133FB17D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الفرض2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{1C79EF4F-64B9-4F11-B671-19E170F641E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الامتحان</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0" shapeId="0" xr:uid="{A51110F8-54CD-4B63-BDBB-8270C48BA19D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>المعدل المرجح</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="0" shapeId="0" xr:uid="{4093612B-F7EB-40B9-B8CE-C9BC39053925}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve"> الرتبة الأولى في القسم</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{D978E3CF-6C4E-4D45-AB23-A4E5F0A7BEEC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve"> الرتبة الاخيرة في القسم</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{E1F225FC-F18E-4C65-9624-4E33B2958EAC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>معدل القسم</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0" xr:uid="{AFDAD97B-33D0-438F-A0E7-F89AA2855EF5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>📖 الوضعية: الطاولة 5 طلبت عدة أطباق. لكل طبق احسب: المبلغ قبل الضريبة (HT)، الضريبة على القيمة المضافة (10%)، والمبلغ شامل الضريبة (TTC). نسبة الضريبة نفسها لجميع الأصناف.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A41" authorId="0" shapeId="0" xr:uid="{CA94E971-CAE4-4485-A7BB-18ADA9A6C3D4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>🟢 المرجع المطلق للضريبة — لأن النسبة ثابتة لجميع الأطباق.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0" xr:uid="{6E03D6BE-A3A1-4078-8C1C-2A530571D6A4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>نسبة الضريبة على القيمة المضافة:</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0" xr:uid="{FAEB69FE-7A63-477D-896E-2DC9BA522E7E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الطبق المطلوب</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0" xr:uid="{01D3A457-ACBF-4E24-9480-5BABB0CB76BA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الثمن قبل الضريبة (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{CB1B5546-7B19-49C2-BEC5-034ADC8958D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الكمية</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{553AFC52-DA9E-4664-854D-696918336148}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>المبلغ قبل الضريبة (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{34B7E46C-D3AA-4B73-8DD0-C0CECAF80FF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الضريبة 10٪ (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{05D6B02F-A319-4426-B50D-2BE8372F8516}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>المبلغ شامل الضريبة (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0" xr:uid="{9A3C548B-26AA-4540-9F42-8BFB07A62F35}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>💰 المجموع الكلي للطاولة 5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A57" authorId="0" shapeId="0" xr:uid="{8B1225B3-C998-4B7D-AB34-B6855BFF3530}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>📖 الوضعية: الشركة تمنح مكافآت حسب الرتبة وربع السنة. املأ جدول الرتبة × الربع باستخدام صيغة واحدة فقط ثم انسخها لبقية الجدول.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0" xr:uid="{C6FCA400-4A86-4602-8531-9C8294F97BBC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الرتبة</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C60" authorId="0" shapeId="0" xr:uid="{0C02D6B5-E62F-4792-BF4D-48A5DDC14826}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الراتب الأساسي (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0" xr:uid="{CD2BBF86-EBE0-4EA6-839F-7401EA8E36BC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>مجموع المكافآت لكل ربع سنة</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A70" authorId="0" shapeId="0" xr:uid="{EFE660C8-5247-4236-A7D6-5DD0C51582CD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>📖 الوضعية: ترغب عائلة في تحليل استهلاكها للكهرباء. كل جهاز له قدرته الكهربائية وساعات استخدامه. سعر الكيلوواط/ساعة ثابت وموحد.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{3414FD03-381F-494F-8C6C-0A2A49CD6944}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>🟢 المرجع المطلق لسعر الكيلوواط/ساعة — لأنه ثابت لجميع الأجهزة.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0" xr:uid="{8D467F43-3CF7-4393-A22B-345888539C9D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>سعر الكيلوواط/ساعة:</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0" xr:uid="{618D374A-179B-4FF1-BEA3-8A6D0E2761F8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الجهاز</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C76" authorId="0" shapeId="0" xr:uid="{920993DF-5FBC-4058-9256-1C1AF63BA703}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>القدرة (واط)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D76" authorId="0" shapeId="0" xr:uid="{B3B4A4AE-3A5C-4E9C-A26D-B4E11A593611}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>عدد الوحدات</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E76" authorId="0" shapeId="0" xr:uid="{DF677633-076B-42ED-8996-EE4A38C8A396}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>ساعات/اليوم</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F76" authorId="0" shapeId="0" xr:uid="{5C55EC30-7F11-4874-B21D-D78CD4AC5D71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الاستهلاك ك.و.س/اليوم</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G76" authorId="0" shapeId="0" xr:uid="{115BD8D9-6D28-409C-9D8D-C218EAFB79A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>التكلفة/اليوم (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H76" authorId="0" shapeId="0" xr:uid="{BF94D73F-ACF8-442C-AC9B-959DB831304E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>التكلفة/الشهر (درهم)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0" xr:uid="{1E3F4861-6F16-4367-88C2-10A21889888E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الإجماليات</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0" xr:uid="{5BABEC4C-5325-4DD2-BFCF-24F5082DE258}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الجهاز الأكثر تكلفة (MAX)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0" xr:uid="{FDBC90DD-FD12-44FC-9D69-87595D5D5148}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>الجهاز الأقل تكلفة (MIN)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A95" authorId="0" shapeId="0" xr:uid="{54349ACE-E5AF-4864-8A36-1603FB0C1EEC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>📖 الوضعية: أنشئ جدولًا 9×9 باستخدام صيغة واحدة فقط في الخانة C97، ثم انسخها لبقية الجدول.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="141">
   <si>
     <t>🛒  Exercice 01 — CAISSIER(ÈRE) AU SUPERMARCHÉ</t>
   </si>
@@ -122,12 +756,6 @@
     <t>🟢 Type de référence : ABSOLUE  —  Les coefficients ne changent JAMAIS.</t>
   </si>
   <si>
-    <t>Coeff. Ctrl 1 :</t>
-  </si>
-  <si>
-    <t>Coeff. Ctrl 2 :</t>
-  </si>
-  <si>
     <t>Coeff. Examen :</t>
   </si>
   <si>
@@ -327,9 +955,6 @@
   </si>
   <si>
     <t>✖️  Exercice 06 — TABLE DE MULTIPLICATION — Référence MIXTE</t>
-  </si>
-  <si>
-    <t>📖 Situation : Crée une table 9×9 avec UNE SEULE formule en C5, puis copie-la dans tout le tableau</t>
   </si>
   <si>
     <t>×</t>
@@ -476,6 +1101,18 @@
   <si>
     <t>Classe:</t>
   </si>
+  <si>
+    <t>Coeff. contrôle 1 :</t>
+  </si>
+  <si>
+    <t>Coeff. contrôle 2 :</t>
+  </si>
+  <si>
+    <t>📖 Situation : Crée une table 9×9 avec UNE SEULE formule en C97, puis copie-la dans tout le tableau</t>
+  </si>
+  <si>
+    <t>خاص بالتصحيح الاتوماتيكي</t>
+  </si>
 </sst>
 </file>
 
@@ -486,7 +1123,7 @@
     <numFmt numFmtId="165" formatCode="#,##0&quot; DH&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -618,13 +1255,6 @@
     <font>
       <sz val="14"/>
       <color rgb="FF0D47A1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -795,8 +1425,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -925,12 +1575,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor rgb="FF70AD47"/>
       </patternFill>
@@ -941,8 +1585,20 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1131,19 +1787,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="dotted">
-        <color indexed="64"/>
-      </left>
-      <right style="dotted">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="dashed">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1210,11 +1853,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1300,32 +2025,32 @@
     <xf numFmtId="2" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="29" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="31" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="28" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="30" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,197 +2059,225 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="33" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="32" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="37" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="38" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="39" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="41" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="42" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="46" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="45" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="40" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="41" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="40" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="41" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="24" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1609,6 +2362,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1789,8 +2546,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M156"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1807,61 +2564,61 @@
     <col min="12" max="12" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="65" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="68" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="68" t="s">
-        <v>129</v>
-      </c>
-      <c r="G1" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="J1" s="66"/>
-    </row>
-    <row r="2" spans="1:11" s="65" customFormat="1" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="J2" s="66"/>
+    <row r="1" spans="1:11" s="60" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="88" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1" s="61"/>
+    </row>
+    <row r="2" spans="1:11" s="60" customFormat="1" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
     </row>
     <row r="4" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
     </row>
     <row r="6" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1915,10 +2672,10 @@
       <c r="F10" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="84" t="s">
+      <c r="J10" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="85"/>
+      <c r="K10" s="68"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
@@ -2029,66 +2786,66 @@
     </row>
     <row r="16" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="63" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="58" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="81"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="107" t="s">
+      <c r="A21" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="102" t="s">
+      <c r="A22" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
     </row>
     <row r="23" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="27" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="C24" s="11">
         <v>1</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="E24" s="11">
         <v>2</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G24" s="11">
         <v>3</v>
@@ -2097,24 +2854,24 @@
     <row r="25" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C27" s="5">
         <v>12</v>
@@ -2128,14 +2885,14 @@
       <c r="F27" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J27" s="84" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="85"/>
+      <c r="J27" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="68"/>
     </row>
     <row r="28" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28" s="9">
         <v>18</v>
@@ -2158,7 +2915,7 @@
     </row>
     <row r="29" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C29" s="5">
         <v>8</v>
@@ -2183,7 +2940,7 @@
     </row>
     <row r="30" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30" s="9">
         <v>15</v>
@@ -2208,7 +2965,7 @@
     </row>
     <row r="31" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="5">
         <v>10</v>
@@ -2233,7 +2990,7 @@
     </row>
     <row r="32" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C32" s="9">
         <v>19</v>
@@ -2258,7 +3015,7 @@
     </row>
     <row r="33" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5">
         <v>14</v>
@@ -2276,63 +3033,63 @@
     <row r="35" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E36" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="72"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="73"/>
+    </row>
+    <row r="40" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="82" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="87" t="s">
+      <c r="B40" s="72"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="73"/>
+    </row>
+    <row r="41" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="82"/>
-    </row>
-    <row r="40" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="103" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="82"/>
-    </row>
-    <row r="41" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="96" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="81"/>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="82"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="73"/>
     </row>
     <row r="42" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="43" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C43" s="14">
         <v>0.1</v>
@@ -2341,31 +3098,31 @@
     <row r="44" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="E45" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="F45" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="G45" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="J45" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="G45" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J45" s="84" t="s">
-        <v>53</v>
-      </c>
-      <c r="K45" s="85"/>
+      <c r="K45" s="68"/>
     </row>
     <row r="46" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C46" s="4">
         <v>45</v>
@@ -2391,7 +3148,7 @@
     </row>
     <row r="47" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C47" s="8">
         <v>38</v>
@@ -2419,7 +3176,7 @@
     </row>
     <row r="48" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C48" s="4">
         <v>52</v>
@@ -2447,7 +3204,7 @@
     </row>
     <row r="49" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C49" s="8">
         <v>65</v>
@@ -2475,7 +3232,7 @@
     </row>
     <row r="50" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C50" s="4">
         <v>28</v>
@@ -2503,7 +3260,7 @@
     </row>
     <row r="51" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C51" s="8">
         <v>12</v>
@@ -2531,59 +3288,59 @@
     </row>
     <row r="53" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="54" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="80" t="s">
+      <c r="B54" s="92" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="72"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="72"/>
+      <c r="F56" s="72"/>
+      <c r="G56" s="73"/>
+    </row>
+    <row r="57" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="C54" s="81"/>
-      <c r="D54" s="81"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="86" t="s">
+      <c r="B57" s="72"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="72"/>
+      <c r="G57" s="73"/>
+    </row>
+    <row r="58" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="81"/>
-      <c r="C56" s="81"/>
-      <c r="D56" s="81"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="82"/>
-    </row>
-    <row r="57" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="91" t="s">
-        <v>62</v>
-      </c>
-      <c r="B57" s="81"/>
-      <c r="C57" s="81"/>
-      <c r="D57" s="81"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="81"/>
-      <c r="G57" s="82"/>
-    </row>
-    <row r="58" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="82"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
+      <c r="F58" s="72"/>
+      <c r="G58" s="73"/>
     </row>
     <row r="59" spans="1:11" ht="19.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D60" s="17">
         <v>0.05</v>
@@ -2597,10 +3354,10 @@
       <c r="G60" s="17">
         <v>0.15</v>
       </c>
-      <c r="J60" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="K60" s="85"/>
+      <c r="J60" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="K60" s="68"/>
     </row>
     <row r="61" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J61" s="41" t="s">
@@ -2612,7 +3369,7 @@
     </row>
     <row r="62" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C62" s="18">
         <v>2200</v>
@@ -2640,7 +3397,7 @@
     </row>
     <row r="63" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C63" s="19">
         <v>2400</v>
@@ -2668,7 +3425,7 @@
     </row>
     <row r="64" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C64" s="18">
         <v>3500</v>
@@ -2696,7 +3453,7 @@
     </row>
     <row r="65" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C65" s="19">
         <v>3800</v>
@@ -2724,7 +3481,7 @@
     </row>
     <row r="66" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C66" s="18">
         <v>5000</v>
@@ -2752,7 +3509,7 @@
     </row>
     <row r="67" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C67" s="19">
         <v>5500</v>
@@ -2779,10 +3536,10 @@
       </c>
     </row>
     <row r="68" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="104" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="81"/>
+      <c r="B68" s="83" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="72"/>
       <c r="D68" s="31" t="s">
         <v>10</v>
       </c>
@@ -2805,15 +3562,15 @@
       </c>
     </row>
     <row r="69" spans="1:11" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="94" t="s">
-        <v>74</v>
-      </c>
-      <c r="B69" s="81"/>
-      <c r="C69" s="81"/>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="82"/>
+      <c r="A69" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="72"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
+      <c r="G69" s="73"/>
       <c r="J69" s="43" t="str">
         <f>$B$68</f>
         <v>TOTAL PRIMES PAR TRIMESTRE</v>
@@ -2824,31 +3581,31 @@
       </c>
     </row>
     <row r="70" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="B70" s="81"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="81"/>
-      <c r="E70" s="81"/>
-      <c r="F70" s="81"/>
-      <c r="G70" s="82"/>
+      <c r="A70" s="99" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="72"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="72"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="72"/>
+      <c r="G70" s="73"/>
     </row>
     <row r="71" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="81"/>
-      <c r="G71" s="82"/>
+      <c r="A71" s="93" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="72"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="72"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="72"/>
+      <c r="G71" s="73"/>
     </row>
     <row r="72" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="73" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C73" s="21">
         <v>1.2</v>
@@ -2858,34 +3615,34 @@
     <row r="75" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D76" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C76" s="22" t="s">
+      <c r="E76" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="F76" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="G76" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="F76" s="22" t="s">
+      <c r="H76" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="G76" s="22" t="s">
+      <c r="J76" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="H76" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="J76" s="84" t="s">
-        <v>85</v>
-      </c>
-      <c r="K76" s="85"/>
+      <c r="K76" s="68"/>
     </row>
     <row r="77" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C77" s="5">
         <v>150</v>
@@ -2914,7 +3671,7 @@
     </row>
     <row r="78" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C78" s="9">
         <v>1800</v>
@@ -2945,7 +3702,7 @@
     </row>
     <row r="79" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C79" s="5">
         <v>120</v>
@@ -2976,7 +3733,7 @@
     </row>
     <row r="80" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C80" s="9">
         <v>2000</v>
@@ -3007,7 +3764,7 @@
     </row>
     <row r="81" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C81" s="5">
         <v>1500</v>
@@ -3038,7 +3795,7 @@
     </row>
     <row r="82" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C82" s="9">
         <v>20</v>
@@ -3069,7 +3826,7 @@
     </row>
     <row r="83" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C83" s="5">
         <v>200</v>
@@ -3100,7 +3857,7 @@
     </row>
     <row r="84" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C84" s="9">
         <v>900</v>
@@ -3141,12 +3898,12 @@
     </row>
     <row r="86" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="87" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="108" t="s">
-        <v>94</v>
-      </c>
-      <c r="C87" s="81"/>
-      <c r="D87" s="81"/>
-      <c r="E87" s="81"/>
+      <c r="B87" s="100" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="72"/>
+      <c r="D87" s="72"/>
+      <c r="E87" s="72"/>
       <c r="F87" s="33" t="s">
         <v>10</v>
       </c>
@@ -3168,12 +3925,12 @@
       <c r="H89" s="34"/>
     </row>
     <row r="90" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="99" t="s">
-        <v>95</v>
-      </c>
-      <c r="C90" s="81"/>
-      <c r="D90" s="81"/>
-      <c r="E90" s="81"/>
+      <c r="B90" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="C90" s="72"/>
+      <c r="D90" s="72"/>
+      <c r="E90" s="72"/>
       <c r="F90" s="35" t="s">
         <v>10</v>
       </c>
@@ -3182,12 +3939,12 @@
       <c r="I90" s="34"/>
     </row>
     <row r="91" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="99" t="s">
-        <v>96</v>
-      </c>
-      <c r="C91" s="81"/>
-      <c r="D91" s="81"/>
-      <c r="E91" s="81"/>
+      <c r="B91" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="72"/>
+      <c r="D91" s="72"/>
+      <c r="E91" s="72"/>
       <c r="F91" s="35" t="s">
         <v>10</v>
       </c>
@@ -3197,42 +3954,42 @@
     </row>
     <row r="92" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="97" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" s="81"/>
-      <c r="C94" s="81"/>
-      <c r="D94" s="81"/>
-      <c r="E94" s="81"/>
-      <c r="F94" s="81"/>
-      <c r="G94" s="81"/>
-      <c r="H94" s="81"/>
-      <c r="I94" s="81"/>
-      <c r="J94" s="81"/>
-      <c r="K94" s="81"/>
-      <c r="L94" s="81"/>
-      <c r="M94" s="81"/>
+      <c r="A94" s="76" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="72"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="72"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
+      <c r="G94" s="72"/>
+      <c r="H94" s="72"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="72"/>
+      <c r="M94" s="72"/>
     </row>
     <row r="95" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="95" t="s">
-        <v>98</v>
-      </c>
-      <c r="B95" s="81"/>
-      <c r="C95" s="81"/>
-      <c r="D95" s="81"/>
-      <c r="E95" s="81"/>
-      <c r="F95" s="81"/>
-      <c r="G95" s="81"/>
-      <c r="H95" s="81"/>
-      <c r="I95" s="81"/>
-      <c r="J95" s="81"/>
-      <c r="K95" s="81"/>
-      <c r="L95" s="81"/>
-      <c r="M95" s="81"/>
+      <c r="A95" s="74" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
+      <c r="F95" s="72"/>
+      <c r="G95" s="72"/>
+      <c r="H95" s="72"/>
+      <c r="I95" s="72"/>
+      <c r="J95" s="72"/>
+      <c r="K95" s="72"/>
+      <c r="L95" s="72"/>
+      <c r="M95" s="72"/>
     </row>
     <row r="96" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C96" s="24">
         <v>1</v>
@@ -3551,10 +4308,10 @@
       </c>
     </row>
     <row r="110" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D110" s="84" t="s">
-        <v>100</v>
-      </c>
-      <c r="E110" s="85"/>
+      <c r="D110" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="E110" s="68"/>
     </row>
     <row r="111" spans="2:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D111" s="41" t="s">
@@ -3574,7 +4331,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="46"/>
       <c r="D113" s="49">
         <v>2</v>
@@ -3584,7 +4341,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="46"/>
       <c r="D114" s="48">
         <v>3</v>
@@ -3594,7 +4351,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="46"/>
       <c r="D115" s="49">
         <v>4</v>
@@ -3604,7 +4361,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="46"/>
       <c r="D116" s="48">
         <v>5</v>
@@ -3614,7 +4371,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="46"/>
       <c r="D117" s="49">
         <v>6</v>
@@ -3624,7 +4381,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="46"/>
       <c r="D118" s="50">
         <v>7</v>
@@ -3634,7 +4391,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C119" s="46"/>
       <c r="D119" s="51">
         <v>8</v>
@@ -3644,356 +4401,563 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C120" s="46"/>
-      <c r="D120" s="52">
+      <c r="D120" s="102">
         <v>9</v>
       </c>
-      <c r="E120" s="47" t="str">
+      <c r="E120" s="103" t="str">
         <f t="shared" si="0"/>
         <v>❌</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="100" t="s">
-        <v>101</v>
-      </c>
-      <c r="B123" s="79"/>
-      <c r="C123" s="79"/>
-      <c r="D123" s="79"/>
-      <c r="E123" s="79"/>
-      <c r="F123" s="79"/>
-      <c r="G123" s="79"/>
-      <c r="H123" s="79"/>
-    </row>
-    <row r="124" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="69" t="s">
-        <v>137</v>
-      </c>
-      <c r="B124" s="70">
+    <row r="121" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="104" t="s">
+        <v>140</v>
+      </c>
+      <c r="B121" s="105"/>
+      <c r="C121" s="105"/>
+      <c r="D121" s="105"/>
+      <c r="E121" s="105"/>
+      <c r="F121" s="105"/>
+      <c r="G121" s="105"/>
+      <c r="H121" s="105"/>
+      <c r="I121" s="105"/>
+      <c r="J121" s="106"/>
+    </row>
+    <row r="122" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="107"/>
+      <c r="B122" s="108"/>
+      <c r="C122" s="108"/>
+      <c r="D122" s="108"/>
+      <c r="E122" s="108"/>
+      <c r="F122" s="108"/>
+      <c r="G122" s="108"/>
+      <c r="H122" s="108"/>
+      <c r="I122" s="108"/>
+      <c r="J122" s="117"/>
+    </row>
+    <row r="123" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B123" s="70"/>
+      <c r="C123" s="70"/>
+      <c r="D123" s="70"/>
+      <c r="E123" s="70"/>
+      <c r="F123" s="70"/>
+      <c r="G123" s="70"/>
+      <c r="H123" s="70"/>
+      <c r="I123" s="110"/>
+      <c r="J123" s="118" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="B124" s="65">
         <f ca="1">TODAY()</f>
         <v>46078</v>
       </c>
-      <c r="C124" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="D124" s="73" t="str">
+      <c r="C124" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D124" s="89" t="str">
         <f>C1</f>
         <v>…................................…......+..........................................</v>
       </c>
-      <c r="E124" s="74"/>
-      <c r="F124" s="75"/>
-      <c r="G124" s="70" t="s">
-        <v>139</v>
-      </c>
-      <c r="H124" s="71" t="str">
+      <c r="E124" s="90"/>
+      <c r="F124" s="91"/>
+      <c r="G124" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="H124" s="66" t="str">
         <f>G1</f>
-        <v>2/5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="53" t="s">
+        <v>2/1</v>
+      </c>
+      <c r="I124" s="110"/>
+      <c r="J124" s="118"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="110"/>
+      <c r="B125" s="110"/>
+      <c r="C125" s="110"/>
+      <c r="D125" s="110"/>
+      <c r="E125" s="110"/>
+      <c r="F125" s="110"/>
+      <c r="G125" s="110"/>
+      <c r="H125" s="110"/>
+      <c r="I125" s="110"/>
+      <c r="J125" s="118"/>
+    </row>
+    <row r="126" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="110"/>
+      <c r="B126" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="D126" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="E126" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C126" s="53" t="s">
+      <c r="F126" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="D126" s="53" t="s">
+      <c r="G126" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E126" s="53" t="s">
+      <c r="H126" s="110"/>
+      <c r="I126" s="110"/>
+      <c r="J126" s="118"/>
+    </row>
+    <row r="127" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A127" s="110"/>
+      <c r="B127" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="F126" s="53" t="s">
+      <c r="C127" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="G126" s="53" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B127" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="C127" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="D127" s="54">
+      <c r="D127" s="53">
         <v>2</v>
       </c>
-      <c r="E127" s="54">
+      <c r="E127" s="53">
         <f>COUNTIF(K12:K13,"✅")</f>
         <v>0</v>
       </c>
-      <c r="F127" s="55">
+      <c r="F127" s="54">
         <f>E127/D127</f>
         <v>0</v>
       </c>
-      <c r="G127" s="56">
+      <c r="G127" s="55">
         <f>F127*D127</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B128" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="C128" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="D128" s="54">
+      <c r="H127" s="110"/>
+      <c r="I127" s="110"/>
+      <c r="J127" s="118"/>
+    </row>
+    <row r="128" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A128" s="110"/>
+      <c r="B128" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="C128" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D128" s="53">
         <v>4</v>
       </c>
-      <c r="E128" s="54">
+      <c r="E128" s="53">
         <f>COUNTIF(K29:K32,"✅")</f>
         <v>0</v>
       </c>
-      <c r="F128" s="55">
+      <c r="F128" s="54">
         <f t="shared" ref="F128:F132" si="1">E128/D128</f>
         <v>0</v>
       </c>
-      <c r="G128" s="56">
+      <c r="G128" s="55">
         <f t="shared" ref="G128:G132" si="2">F128*D128</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B129" s="61" t="s">
-        <v>112</v>
-      </c>
-      <c r="C129" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="D129" s="54">
+      <c r="H128" s="110"/>
+      <c r="I128" s="110"/>
+      <c r="J128" s="118"/>
+    </row>
+    <row r="129" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A129" s="110"/>
+      <c r="B129" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C129" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D129" s="53">
         <v>5</v>
       </c>
-      <c r="E129" s="54">
+      <c r="E129" s="53">
         <f>COUNTIF(K47:K51,"✅")</f>
         <v>0</v>
       </c>
-      <c r="F129" s="55">
+      <c r="F129" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G129" s="56">
+      <c r="G129" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B130" s="61" t="s">
-        <v>113</v>
-      </c>
-      <c r="C130" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D130" s="54">
+      <c r="H129" s="110"/>
+      <c r="I129" s="110"/>
+      <c r="J129" s="118"/>
+    </row>
+    <row r="130" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A130" s="110"/>
+      <c r="B130" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C130" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D130" s="53">
         <v>8</v>
       </c>
-      <c r="E130" s="54">
+      <c r="E130" s="53">
         <f>COUNTIF(K62:K69,"✅")</f>
         <v>0</v>
       </c>
-      <c r="F130" s="55">
+      <c r="F130" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G130" s="56">
+      <c r="G130" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B131" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C131" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="D131" s="54">
+      <c r="H130" s="110"/>
+      <c r="I130" s="110"/>
+      <c r="J130" s="118"/>
+    </row>
+    <row r="131" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A131" s="110"/>
+      <c r="B131" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="C131" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D131" s="53">
         <v>8</v>
       </c>
-      <c r="E131" s="54">
+      <c r="E131" s="53">
         <f>COUNTIF(K78:K85,"✅")</f>
         <v>0</v>
       </c>
-      <c r="F131" s="55">
+      <c r="F131" s="54">
         <f>E131/D131</f>
         <v>0</v>
       </c>
-      <c r="G131" s="56">
+      <c r="G131" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B132" s="61" t="s">
-        <v>116</v>
-      </c>
-      <c r="C132" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="D132" s="54">
+      <c r="H131" s="110"/>
+      <c r="I131" s="110"/>
+      <c r="J131" s="118"/>
+    </row>
+    <row r="132" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A132" s="110"/>
+      <c r="B132" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C132" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="D132" s="53">
         <v>9</v>
       </c>
-      <c r="E132" s="54">
+      <c r="E132" s="53">
         <f>COUNTIF(E112:E120,"✅")</f>
         <v>0</v>
       </c>
-      <c r="F132" s="55">
+      <c r="F132" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G132" s="56">
+      <c r="G132" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" spans="1:8" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="F134" s="76" t="s">
-        <v>117</v>
-      </c>
-      <c r="G134" s="77"/>
-    </row>
-    <row r="135" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="F135" s="57">
+      <c r="H132" s="110"/>
+      <c r="I132" s="110"/>
+      <c r="J132" s="118"/>
+    </row>
+    <row r="133" spans="1:10" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="110"/>
+      <c r="B133" s="110"/>
+      <c r="C133" s="110"/>
+      <c r="D133" s="110"/>
+      <c r="E133" s="110"/>
+      <c r="H133" s="110"/>
+      <c r="I133" s="110"/>
+      <c r="J133" s="118"/>
+    </row>
+    <row r="134" spans="1:10" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A134" s="110"/>
+      <c r="B134" s="110"/>
+      <c r="C134" s="110"/>
+      <c r="D134" s="110"/>
+      <c r="E134" s="110"/>
+      <c r="F134" s="113" t="s">
+        <v>114</v>
+      </c>
+      <c r="G134" s="114"/>
+      <c r="H134" s="110"/>
+      <c r="I134" s="110"/>
+      <c r="J134" s="118"/>
+    </row>
+    <row r="135" spans="1:10" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A135" s="110"/>
+      <c r="B135" s="110"/>
+      <c r="C135" s="110"/>
+      <c r="D135" s="110"/>
+      <c r="E135" s="110"/>
+      <c r="F135" s="115">
         <f>SUMPRODUCT(F127:F132,D127:D132)/SUM(D127:D132)</f>
         <v>0</v>
       </c>
-      <c r="G135" s="58">
+      <c r="G135" s="116">
         <f>SUM(G127:G132)/SUM(D127:D132)*20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="E136" s="59"/>
-      <c r="F136" s="60"/>
-    </row>
-    <row r="137" spans="1:8" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="98" t="s">
+      <c r="H135" s="110"/>
+      <c r="I135" s="110"/>
+      <c r="J135" s="118"/>
+    </row>
+    <row r="136" spans="1:10" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A136" s="110"/>
+      <c r="B136" s="110"/>
+      <c r="C136" s="110"/>
+      <c r="D136" s="110"/>
+      <c r="E136" s="111"/>
+      <c r="F136" s="112"/>
+      <c r="G136" s="110"/>
+      <c r="H136" s="110"/>
+      <c r="I136" s="110"/>
+      <c r="J136" s="118"/>
+    </row>
+    <row r="137" spans="1:10" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="B137" s="70"/>
+      <c r="C137" s="70"/>
+      <c r="D137" s="70"/>
+      <c r="E137" s="70"/>
+      <c r="F137" s="70"/>
+      <c r="G137" s="70"/>
+      <c r="H137" s="70"/>
+      <c r="I137" s="110"/>
+      <c r="J137" s="118"/>
+    </row>
+    <row r="138" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C138" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="I138" s="110"/>
+      <c r="J138" s="118"/>
+    </row>
+    <row r="139" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C139" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="I139" s="110"/>
+      <c r="J139" s="118"/>
+    </row>
+    <row r="140" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C140" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="B137" s="79"/>
-      <c r="C137" s="79"/>
-      <c r="D137" s="79"/>
-      <c r="E137" s="79"/>
-      <c r="F137" s="79"/>
-      <c r="G137" s="79"/>
-      <c r="H137" s="79"/>
-    </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C138" s="64" t="s">
+      <c r="I140" s="110"/>
+      <c r="J140" s="118"/>
+    </row>
+    <row r="141" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C141" s="59" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C139" s="64" t="s">
+      <c r="I141" s="110"/>
+      <c r="J141" s="118"/>
+    </row>
+    <row r="142" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C142" s="59" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C140" s="64" t="s">
+      <c r="I142" s="110"/>
+      <c r="J142" s="118"/>
+    </row>
+    <row r="143" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C143" s="59" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C141" s="64" t="s">
+      <c r="I143" s="110"/>
+      <c r="J143" s="118"/>
+    </row>
+    <row r="144" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C144" s="59" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C142" s="64" t="s">
+      <c r="I144" s="110"/>
+      <c r="J144" s="118"/>
+    </row>
+    <row r="145" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="59" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C143" s="64" t="s">
+      <c r="I145" s="110"/>
+      <c r="J145" s="118"/>
+    </row>
+    <row r="146" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="59" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C144" s="64" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C145" s="64" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C146" s="64" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="64"/>
-    </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C148" s="64"/>
-    </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C149" s="64"/>
-    </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C150" s="64"/>
-    </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="152" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A152" s="101" t="s">
-        <v>136</v>
-      </c>
-      <c r="B152" s="79"/>
-      <c r="C152" s="79"/>
-      <c r="D152" s="79"/>
-      <c r="E152" s="79"/>
-      <c r="F152" s="79"/>
-      <c r="G152" s="79"/>
-      <c r="H152" s="79"/>
-    </row>
-    <row r="153" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="93"/>
-      <c r="B153" s="79"/>
-      <c r="C153" s="79"/>
-      <c r="D153" s="79"/>
-      <c r="E153" s="79"/>
-      <c r="F153" s="79"/>
-      <c r="G153" s="79"/>
-      <c r="H153" s="79"/>
-    </row>
-    <row r="154" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="79"/>
-      <c r="B154" s="79"/>
-      <c r="C154" s="79"/>
-      <c r="D154" s="79"/>
-      <c r="E154" s="79"/>
-      <c r="F154" s="79"/>
-      <c r="G154" s="79"/>
-      <c r="H154" s="79"/>
-    </row>
-    <row r="155" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="79"/>
-      <c r="B155" s="79"/>
-      <c r="C155" s="79"/>
-      <c r="D155" s="79"/>
-      <c r="E155" s="79"/>
-      <c r="F155" s="79"/>
-      <c r="G155" s="79"/>
-      <c r="H155" s="79"/>
-    </row>
-    <row r="156" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="79"/>
-      <c r="B156" s="79"/>
-      <c r="C156" s="79"/>
-      <c r="D156" s="79"/>
-      <c r="E156" s="79"/>
-      <c r="F156" s="79"/>
-      <c r="G156" s="79"/>
-      <c r="H156" s="79"/>
+      <c r="I146" s="110"/>
+      <c r="J146" s="118"/>
+    </row>
+    <row r="147" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="59"/>
+      <c r="I147" s="110"/>
+      <c r="J147" s="118"/>
+    </row>
+    <row r="148" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="59"/>
+      <c r="I148" s="110"/>
+      <c r="J148" s="118"/>
+    </row>
+    <row r="149" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C149" s="59"/>
+      <c r="I149" s="110"/>
+      <c r="J149" s="118"/>
+    </row>
+    <row r="150" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C150" s="59"/>
+      <c r="I150" s="110"/>
+      <c r="J150" s="118"/>
+    </row>
+    <row r="151" spans="1:10" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I151" s="110"/>
+      <c r="J151" s="118"/>
+    </row>
+    <row r="152" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A152" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B152" s="70"/>
+      <c r="C152" s="70"/>
+      <c r="D152" s="70"/>
+      <c r="E152" s="70"/>
+      <c r="F152" s="70"/>
+      <c r="G152" s="70"/>
+      <c r="H152" s="70"/>
+      <c r="I152" s="110"/>
+      <c r="J152" s="118"/>
+    </row>
+    <row r="153" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="69"/>
+      <c r="B153" s="70"/>
+      <c r="C153" s="70"/>
+      <c r="D153" s="70"/>
+      <c r="E153" s="70"/>
+      <c r="F153" s="70"/>
+      <c r="G153" s="70"/>
+      <c r="H153" s="70"/>
+      <c r="I153" s="110"/>
+      <c r="J153" s="118"/>
+    </row>
+    <row r="154" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="70"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="70"/>
+      <c r="E154" s="70"/>
+      <c r="F154" s="70"/>
+      <c r="G154" s="70"/>
+      <c r="H154" s="70"/>
+      <c r="I154" s="110"/>
+      <c r="J154" s="118"/>
+    </row>
+    <row r="155" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="70"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="70"/>
+      <c r="E155" s="70"/>
+      <c r="F155" s="70"/>
+      <c r="G155" s="70"/>
+      <c r="H155" s="70"/>
+      <c r="I155" s="110"/>
+      <c r="J155" s="118"/>
+    </row>
+    <row r="156" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="70"/>
+      <c r="B156" s="70"/>
+      <c r="C156" s="70"/>
+      <c r="D156" s="70"/>
+      <c r="E156" s="70"/>
+      <c r="F156" s="70"/>
+      <c r="G156" s="70"/>
+      <c r="H156" s="70"/>
+      <c r="I156" s="110"/>
+      <c r="J156" s="118"/>
+    </row>
+    <row r="157" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="110"/>
+      <c r="B157" s="110"/>
+      <c r="C157" s="110"/>
+      <c r="D157" s="110"/>
+      <c r="E157" s="110"/>
+      <c r="F157" s="110"/>
+      <c r="G157" s="110"/>
+      <c r="H157" s="110"/>
+      <c r="I157" s="110"/>
+      <c r="J157" s="118"/>
+    </row>
+    <row r="158" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="104" t="s">
+        <v>140</v>
+      </c>
+      <c r="B158" s="105"/>
+      <c r="C158" s="105"/>
+      <c r="D158" s="105"/>
+      <c r="E158" s="105"/>
+      <c r="F158" s="105"/>
+      <c r="G158" s="105"/>
+      <c r="H158" s="105"/>
+      <c r="I158" s="105"/>
+      <c r="J158" s="117"/>
+    </row>
+    <row r="159" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="107"/>
+      <c r="B159" s="108"/>
+      <c r="C159" s="108"/>
+      <c r="D159" s="108"/>
+      <c r="E159" s="108"/>
+      <c r="F159" s="108"/>
+      <c r="G159" s="108"/>
+      <c r="H159" s="108"/>
+      <c r="I159" s="108"/>
+      <c r="J159" s="109"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="39">
+    <mergeCell ref="A121:J122"/>
+    <mergeCell ref="A158:J159"/>
+    <mergeCell ref="J123:J157"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="J60:K60"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="A153:H156"/>
@@ -4010,28 +4974,8 @@
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="B68:C68"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B87:E87"/>
   </mergeCells>
-  <phoneticPr fontId="43" type="noConversion"/>
+  <phoneticPr fontId="42" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{8893F3B3-AF37-4574-A1AF-77D555B47EAF}">
       <formula1>$C$138:$C$146</formula1>
@@ -4039,5 +4983,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>